--- a/output/pdf_financials_xlsx/CRIV.xlsx
+++ b/output/pdf_financials_xlsx/CRIV.xlsx
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.122389</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.030781</v>
       </c>
     </row>
     <row r="119">
@@ -3278,7 +3278,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>-0.122389</v>
       </c>

--- a/output/pdf_financials_xlsx/CRIV.xlsx
+++ b/output/pdf_financials_xlsx/CRIV.xlsx
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.032022</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
         <v>-0.417546</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.543787</v>
+        <v>-0.575809</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.199042</v>
@@ -898,7 +898,7 @@
         <v>-0.417546</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.543787</v>
+        <v>-0.575809</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.199042</v>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.834738</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.298526</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.157394</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.834738</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.298526</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.157394</v>
       </c>
     </row>
     <row r="37">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.834738</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.298526</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.157394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">

--- a/output/pdf_financials_xlsx/CRIV.xlsx
+++ b/output/pdf_financials_xlsx/CRIV.xlsx
@@ -1512,13 +1512,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.028533</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.048393</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.033405</v>
       </c>
     </row>
     <row r="68">
